--- a/Codigos_resNet/datos/deuda multilaterales.xlsx
+++ b/Codigos_resNet/datos/deuda multilaterales.xlsx
@@ -8,13 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\VJaroszewski-econ\Codigos_resNet\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00BD0E29-91A0-47CF-99F2-7A758A963EFB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{668FFDC7-651D-4C19-8D60-06CF07FD4378}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{CAA6EF67-7BC3-4A65-9827-9E2B82094EBF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{CAA6EF67-7BC3-4A65-9827-9E2B82094EBF}"/>
   </bookViews>
   <sheets>
     <sheet name="deuMult" sheetId="1" r:id="rId1"/>
-    <sheet name="dep y encajes" sheetId="2" r:id="rId2"/>
+    <sheet name="bopreal_1" sheetId="3" r:id="rId2"/>
+    <sheet name="bopleal_2" sheetId="4" r:id="rId3"/>
+    <sheet name="bopleal_3" sheetId="5" r:id="rId4"/>
+    <sheet name="bopreal_4" sheetId="6" r:id="rId5"/>
+    <sheet name="dep y encajes" sheetId="2" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="9">
   <si>
     <t>fecha</t>
   </si>
@@ -48,36 +52,40 @@
   <si>
     <t>encajes_ext_p</t>
   </si>
+  <si>
+    <t>bopreal_1</t>
+  </si>
+  <si>
+    <t>FFj</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="24">
+  <numFmts count="22">
     <numFmt numFmtId="42" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0\ _P_t_a_-;\-* #,##0\ _P_t_a_-;_-* &quot;-&quot;\ _P_t_a_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="170" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;-&quot;\ _€_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="172" formatCode="_-* #,##0\ _P_t_s_-;\-* #,##0\ _P_t_s_-;_-* &quot;-&quot;\ _P_t_s_-;_-@_-"/>
-    <numFmt numFmtId="173" formatCode="_-* #,##0.00\ _P_t_s_-;\-* #,##0.00\ _P_t_s_-;_-* &quot;-&quot;??\ _P_t_s_-;_-@_-"/>
-    <numFmt numFmtId="180" formatCode="#,##0,;\-\ #,##0,;&quot;--- &quot;"/>
-    <numFmt numFmtId="181" formatCode="#,##0,,;\-\ #,##0,,;&quot;--- &quot;"/>
-    <numFmt numFmtId="182" formatCode="#,##0.00_);\(#,##0.00\);&quot; --- &quot;"/>
-    <numFmt numFmtId="183" formatCode="_(* #,##0.0000000_);_(* \(#,##0.0000000\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="185" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="188" formatCode="#,"/>
-    <numFmt numFmtId="190" formatCode="_-* #,##0\ _$_-;\-* #,##0\ _$_-;_-* &quot;-&quot;\ _$_-;_-@_-"/>
-    <numFmt numFmtId="193" formatCode="_-* #,##0.00\ _P_t_a_-;\-* #,##0.00\ _P_t_a_-;_-* &quot;-&quot;??\ _P_t_a_-;_-@_-"/>
-    <numFmt numFmtId="194" formatCode="_ * #,##0.0000_ ;_ * \-#,##0.0000_ ;_ * &quot;-&quot;????_ ;_ @_ "/>
-    <numFmt numFmtId="198" formatCode="_-* #,##0.00\ [$€]_-;\-* #,##0.00\ [$€]_-;_-* &quot;-&quot;??\ [$€]_-;_-@_-"/>
-    <numFmt numFmtId="199" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;????_ ;_ @_ "/>
-    <numFmt numFmtId="230" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;-&quot;\ _€_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0\ _P_t_s_-;\-* #,##0\ _P_t_s_-;_-* &quot;-&quot;\ _P_t_s_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="_-* #,##0.00\ _P_t_s_-;\-* #,##0.00\ _P_t_s_-;_-* &quot;-&quot;??\ _P_t_s_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="#,##0,;\-\ #,##0,;&quot;--- &quot;"/>
+    <numFmt numFmtId="171" formatCode="#,##0,,;\-\ #,##0,,;&quot;--- &quot;"/>
+    <numFmt numFmtId="172" formatCode="#,##0.00_);\(#,##0.00\);&quot; --- &quot;"/>
+    <numFmt numFmtId="173" formatCode="_(* #,##0.0000000_);_(* \(#,##0.0000000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="174" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="175" formatCode="#,"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0\ _$_-;\-* #,##0\ _$_-;_-* &quot;-&quot;\ _$_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00\ _P_t_a_-;\-* #,##0.00\ _P_t_a_-;_-* &quot;-&quot;??\ _P_t_a_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0.0000_ ;_ * \-#,##0.0000_ ;_ * &quot;-&quot;????_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-* #,##0.00\ [$€]_-;\-* #,##0.00\ [$€]_-;_-* &quot;-&quot;??\ [$€]_-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;????_ ;_ @_ "/>
+    <numFmt numFmtId="181" formatCode="0.0000"/>
   </numFmts>
   <fonts count="37">
     <font>
@@ -315,7 +323,7 @@
       <name val="Roboto"/>
     </font>
   </fonts>
-  <fills count="27">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -445,6 +453,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -656,9 +670,9 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="24" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="180" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -708,14 +722,14 @@
     <xf numFmtId="0" fontId="19" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="15" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="182" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="188" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="175" fontId="12" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
@@ -914,10 +928,10 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="182" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="182" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="182" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="182" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
@@ -994,48 +1008,48 @@
     <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="194" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="198" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="198" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="198" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="198" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="190" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="193" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -1054,22 +1068,22 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="199" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="194" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1079,10 +1093,10 @@
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1093,7 +1107,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -1102,7 +1116,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1110,7 +1124,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1118,45 +1132,45 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="199" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="199" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="194" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="194" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="194" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="185" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -1165,7 +1179,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1173,7 +1187,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1181,17 +1195,17 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -1200,7 +1214,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1208,7 +1222,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1216,37 +1230,37 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="185" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -1255,7 +1269,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1263,7 +1277,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1271,17 +1285,17 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -1290,7 +1304,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1298,7 +1312,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1306,27 +1320,29 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="185" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="230" fontId="36" fillId="22" borderId="0" xfId="617" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="181" fontId="36" fillId="22" borderId="0" xfId="617" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="36" fillId="22" borderId="0" xfId="617" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="693">
     <cellStyle name="20% - Accent1" xfId="4" xr:uid="{DFDBF0D3-4484-4FCA-A994-E23AD0A68789}"/>
@@ -3006,6 +3022,413 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE5ACFD8-1C39-424F-A292-390C10723097}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="7">
+        <v>45296</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="7">
+        <v>45566</v>
+      </c>
+      <c r="B3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="7">
+        <f>+A3+180</f>
+        <v>45746</v>
+      </c>
+      <c r="B4">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="7">
+        <f t="shared" ref="A5:A8" si="0">+A4+180</f>
+        <v>45926</v>
+      </c>
+      <c r="B5">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="7">
+        <f t="shared" si="0"/>
+        <v>46106</v>
+      </c>
+      <c r="B6">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="7">
+        <f t="shared" si="0"/>
+        <v>46286</v>
+      </c>
+      <c r="B7">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="7">
+        <f t="shared" si="0"/>
+        <v>46466</v>
+      </c>
+      <c r="B8">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="7">
+        <v>46478</v>
+      </c>
+      <c r="B9">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="7">
+        <f>+A8+180</f>
+        <v>46646</v>
+      </c>
+      <c r="B10">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="7">
+        <v>46661</v>
+      </c>
+      <c r="B11">
+        <v>2625</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAD810BA-9103-4DE8-81D0-8B7B80A597F5}">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="7">
+        <v>45338</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="7">
+        <v>45503</v>
+      </c>
+      <c r="B3">
+        <v>166.66666666666666</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="7">
+        <v>45534</v>
+      </c>
+      <c r="B4">
+        <v>166.66666666666666</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="7">
+        <v>45565</v>
+      </c>
+      <c r="B5">
+        <v>166.66666666666666</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="7">
+        <v>45595</v>
+      </c>
+      <c r="B6">
+        <v>166.66666666666666</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="7">
+        <v>45626</v>
+      </c>
+      <c r="B7">
+        <v>166.66666666666666</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="7">
+        <v>45656</v>
+      </c>
+      <c r="B8">
+        <v>166.66666666666666</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="7">
+        <v>45687</v>
+      </c>
+      <c r="B9">
+        <v>166.66666666666666</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="7">
+        <v>45716</v>
+      </c>
+      <c r="B10">
+        <v>166.66666666666666</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="7">
+        <v>45746</v>
+      </c>
+      <c r="B11">
+        <v>166.66666666666666</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="7">
+        <v>45777</v>
+      </c>
+      <c r="B12">
+        <v>166.66666666666666</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="7">
+        <v>45807</v>
+      </c>
+      <c r="B13">
+        <v>166.66666666666666</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="7">
+        <v>45838</v>
+      </c>
+      <c r="B14">
+        <v>166.66666666666666</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{912B4684-C238-4F28-813B-72F0E2928739}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="7">
+        <v>45296</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="7">
+        <v>45534</v>
+      </c>
+      <c r="B3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="7">
+        <v>45626</v>
+      </c>
+      <c r="B4">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="7">
+        <v>45716</v>
+      </c>
+      <c r="B5">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="7">
+        <v>45807</v>
+      </c>
+      <c r="B6">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="7">
+        <v>45899</v>
+      </c>
+      <c r="B7">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="7">
+        <v>45991</v>
+      </c>
+      <c r="B8">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="7">
+        <v>46081</v>
+      </c>
+      <c r="B9">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="7">
+        <v>46173</v>
+      </c>
+      <c r="B10">
+        <v>1050</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54D6D83E-DB14-4B92-98F5-FBCBC28443B2}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="7">
+        <v>45832</v>
+      </c>
+      <c r="B2">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="7">
+        <v>45961</v>
+      </c>
+      <c r="B3">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B4">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="7">
+        <v>46326</v>
+      </c>
+      <c r="B5">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="7">
+        <v>46507</v>
+      </c>
+      <c r="B6">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="7">
+        <v>46691</v>
+      </c>
+      <c r="B7">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="7">
+        <v>46873</v>
+      </c>
+      <c r="B8">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="7">
+        <v>47057</v>
+      </c>
+      <c r="B9">
+        <v>913.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66326B90-32E5-4EC9-AB59-9078B62DF326}">
   <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
